--- a/src/main/resources/Permanent Records.xlsx
+++ b/src/main/resources/Permanent Records.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7449E196-F880-4A21-947D-623F90D8D7B1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D319FD2-0C25-4C74-8A0C-DE19BED7F2C9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
@@ -143,9 +143,6 @@
     <t>Complete Review Process and approve FDM</t>
   </si>
   <si>
-    <t>Under Strategic goals and Objectives- Create 1. Automation Permanent Strategic Goal and	Automation Permanent Objective 2. Automation Permanent Strategic Goal2 and Automation Permanent Objetives 2</t>
-  </si>
-  <si>
     <t>Only Record created by EXE profile User</t>
   </si>
   <si>
@@ -285,6 +282,9 @@
   </si>
   <si>
     <t>Select Match Required =Yes, Is Detailed Budget Required on the Subaward? - Yes,  Non - construction while grant creation</t>
+  </si>
+  <si>
+    <t>Under Strategic goals and Objectives- Create 1. Automation Permanent Strategic Goal and	Automation Permanent Objective 2. Automation Permanent Strategic Goal2 and Automation Permanent Objective2</t>
   </si>
 </sst>
 </file>
@@ -1184,7 +1184,7 @@
         <v>14</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>37</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -1196,7 +1196,7 @@
         <v>16</v>
       </c>
       <c r="D11" s="42" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1215,7 +1215,7 @@
         <v>19</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" s="17" t="s">
         <v>33</v>
@@ -1238,7 +1238,7 @@
         <v>21</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1248,7 +1248,7 @@
         <v>22</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1260,7 +1260,7 @@
         <v>20</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -1272,7 +1272,7 @@
         <v>24</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -1282,7 +1282,7 @@
         <v>25</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1311,129 +1311,129 @@
     </row>
     <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="B25" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25" s="27" t="s">
+      <c r="D25" s="29" t="s">
         <v>65</v>
-      </c>
-      <c r="D25" s="29" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C26" s="26" t="s">
         <v>0</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C27" s="26" t="s">
         <v>0</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C28" s="28"/>
       <c r="D28" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C30" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="D30" s="14" t="s">
         <v>70</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C31" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="D31" s="14" t="s">
         <v>72</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="39" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -1443,50 +1443,50 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" s="32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C41" s="31"/>
       <c r="D41" s="31"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" s="32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C42" s="31"/>
       <c r="D42" s="31"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" s="32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C43" s="31"/>
       <c r="D43" s="31"/>
     </row>
     <row r="44" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44" s="32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C44" s="31"/>
       <c r="D44" s="31"/>
     </row>
     <row r="45" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B45" s="32" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C45" s="31"/>
       <c r="D45" s="31"/>
